--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_11-10-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_11-10-2025.xlsx
@@ -592,25 +592,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7799ae955+80021]
-	GetHandleVerifier [0x0x7ff7799ae9b0+80112]
-	(No symbol) [0x0x7ff77973060f]
-	(No symbol) [0x0x7ff779788854]
-	(No symbol) [0x0x7ff779788b1c]
-	(No symbol) [0x0x7ff7797dc927]
-	(No symbol) [0x0x7ff7797b126f]
-	(No symbol) [0x0x7ff7797d968a]
-	(No symbol) [0x0x7ff7797b1003]
-	(No symbol) [0x0x7ff7797795d1]
-	(No symbol) [0x0x7ff77977a3f3]
-	GetHandleVerifier [0x0x7ff779c6dd0d+2960461]
-	GetHandleVerifier [0x0x7ff779c67fca+2936586]
-	GetHandleVerifier [0x0x7ff779c88a07+3070279]
-	GetHandleVerifier [0x0x7ff7799c843e+185214]
-	GetHandleVerifier [0x0x7ff7799cfe8f+216527]
-	GetHandleVerifier [0x0x7ff7799b7b94+117460]
-	GetHandleVerifier [0x0x7ff7799b7d4f+117903]
-	GetHandleVerifier [0x0x7ff77999dc28+11112]
+	GetHandleVerifier [0x0x7ff7be93e955+80021]
+	GetHandleVerifier [0x0x7ff7be93e9b0+80112]
+	(No symbol) [0x0x7ff7be6c060f]
+	(No symbol) [0x0x7ff7be718854]
+	(No symbol) [0x0x7ff7be718b1c]
+	(No symbol) [0x0x7ff7be76c927]
+	(No symbol) [0x0x7ff7be74126f]
+	(No symbol) [0x0x7ff7be76968a]
+	(No symbol) [0x0x7ff7be741003]
+	(No symbol) [0x0x7ff7be7095d1]
+	(No symbol) [0x0x7ff7be70a3f3]
+	GetHandleVerifier [0x0x7ff7bebfdd0d+2960461]
+	GetHandleVerifier [0x0x7ff7bebf7fca+2936586]
+	GetHandleVerifier [0x0x7ff7bec18a07+3070279]
+	GetHandleVerifier [0x0x7ff7be95843e+185214]
+	GetHandleVerifier [0x0x7ff7be95fe8f+216527]
+	GetHandleVerifier [0x0x7ff7be947b94+117460]
+	GetHandleVerifier [0x0x7ff7be947d4f+117903]
+	GetHandleVerifier [0x0x7ff7be92dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -714,25 +714,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7799ae955+80021]
-	GetHandleVerifier [0x0x7ff7799ae9b0+80112]
-	(No symbol) [0x0x7ff77973060f]
-	(No symbol) [0x0x7ff779788854]
-	(No symbol) [0x0x7ff779788b1c]
-	(No symbol) [0x0x7ff7797dc927]
-	(No symbol) [0x0x7ff7797b126f]
-	(No symbol) [0x0x7ff7797d968a]
-	(No symbol) [0x0x7ff7797b1003]
-	(No symbol) [0x0x7ff7797795d1]
-	(No symbol) [0x0x7ff77977a3f3]
-	GetHandleVerifier [0x0x7ff779c6dd0d+2960461]
-	GetHandleVerifier [0x0x7ff779c67fca+2936586]
-	GetHandleVerifier [0x0x7ff779c88a07+3070279]
-	GetHandleVerifier [0x0x7ff7799c843e+185214]
-	GetHandleVerifier [0x0x7ff7799cfe8f+216527]
-	GetHandleVerifier [0x0x7ff7799b7b94+117460]
-	GetHandleVerifier [0x0x7ff7799b7d4f+117903]
-	GetHandleVerifier [0x0x7ff77999dc28+11112]
+	GetHandleVerifier [0x0x7ff7be93e955+80021]
+	GetHandleVerifier [0x0x7ff7be93e9b0+80112]
+	(No symbol) [0x0x7ff7be6c060f]
+	(No symbol) [0x0x7ff7be718854]
+	(No symbol) [0x0x7ff7be718b1c]
+	(No symbol) [0x0x7ff7be76c927]
+	(No symbol) [0x0x7ff7be74126f]
+	(No symbol) [0x0x7ff7be76968a]
+	(No symbol) [0x0x7ff7be741003]
+	(No symbol) [0x0x7ff7be7095d1]
+	(No symbol) [0x0x7ff7be70a3f3]
+	GetHandleVerifier [0x0x7ff7bebfdd0d+2960461]
+	GetHandleVerifier [0x0x7ff7bebf7fca+2936586]
+	GetHandleVerifier [0x0x7ff7bec18a07+3070279]
+	GetHandleVerifier [0x0x7ff7be95843e+185214]
+	GetHandleVerifier [0x0x7ff7be95fe8f+216527]
+	GetHandleVerifier [0x0x7ff7be947b94+117460]
+	GetHandleVerifier [0x0x7ff7be947d4f+117903]
+	GetHandleVerifier [0x0x7ff7be92dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -836,25 +836,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7799ae955+80021]
-	GetHandleVerifier [0x0x7ff7799ae9b0+80112]
-	(No symbol) [0x0x7ff77973060f]
-	(No symbol) [0x0x7ff779788854]
-	(No symbol) [0x0x7ff779788b1c]
-	(No symbol) [0x0x7ff7797dc927]
-	(No symbol) [0x0x7ff7797b126f]
-	(No symbol) [0x0x7ff7797d968a]
-	(No symbol) [0x0x7ff7797b1003]
-	(No symbol) [0x0x7ff7797795d1]
-	(No symbol) [0x0x7ff77977a3f3]
-	GetHandleVerifier [0x0x7ff779c6dd0d+2960461]
-	GetHandleVerifier [0x0x7ff779c67fca+2936586]
-	GetHandleVerifier [0x0x7ff779c88a07+3070279]
-	GetHandleVerifier [0x0x7ff7799c843e+185214]
-	GetHandleVerifier [0x0x7ff7799cfe8f+216527]
-	GetHandleVerifier [0x0x7ff7799b7b94+117460]
-	GetHandleVerifier [0x0x7ff7799b7d4f+117903]
-	GetHandleVerifier [0x0x7ff77999dc28+11112]
+	GetHandleVerifier [0x0x7ff7be93e955+80021]
+	GetHandleVerifier [0x0x7ff7be93e9b0+80112]
+	(No symbol) [0x0x7ff7be6c060f]
+	(No symbol) [0x0x7ff7be718854]
+	(No symbol) [0x0x7ff7be718b1c]
+	(No symbol) [0x0x7ff7be76c927]
+	(No symbol) [0x0x7ff7be74126f]
+	(No symbol) [0x0x7ff7be76968a]
+	(No symbol) [0x0x7ff7be741003]
+	(No symbol) [0x0x7ff7be7095d1]
+	(No symbol) [0x0x7ff7be70a3f3]
+	GetHandleVerifier [0x0x7ff7bebfdd0d+2960461]
+	GetHandleVerifier [0x0x7ff7bebf7fca+2936586]
+	GetHandleVerifier [0x0x7ff7bec18a07+3070279]
+	GetHandleVerifier [0x0x7ff7be95843e+185214]
+	GetHandleVerifier [0x0x7ff7be95fe8f+216527]
+	GetHandleVerifier [0x0x7ff7be947b94+117460]
+	GetHandleVerifier [0x0x7ff7be947d4f+117903]
+	GetHandleVerifier [0x0x7ff7be92dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -958,25 +958,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7799ae955+80021]
-	GetHandleVerifier [0x0x7ff7799ae9b0+80112]
-	(No symbol) [0x0x7ff77973060f]
-	(No symbol) [0x0x7ff779788854]
-	(No symbol) [0x0x7ff779788b1c]
-	(No symbol) [0x0x7ff7797dc927]
-	(No symbol) [0x0x7ff7797b126f]
-	(No symbol) [0x0x7ff7797d968a]
-	(No symbol) [0x0x7ff7797b1003]
-	(No symbol) [0x0x7ff7797795d1]
-	(No symbol) [0x0x7ff77977a3f3]
-	GetHandleVerifier [0x0x7ff779c6dd0d+2960461]
-	GetHandleVerifier [0x0x7ff779c67fca+2936586]
-	GetHandleVerifier [0x0x7ff779c88a07+3070279]
-	GetHandleVerifier [0x0x7ff7799c843e+185214]
-	GetHandleVerifier [0x0x7ff7799cfe8f+216527]
-	GetHandleVerifier [0x0x7ff7799b7b94+117460]
-	GetHandleVerifier [0x0x7ff7799b7d4f+117903]
-	GetHandleVerifier [0x0x7ff77999dc28+11112]
+	GetHandleVerifier [0x0x7ff7be93e955+80021]
+	GetHandleVerifier [0x0x7ff7be93e9b0+80112]
+	(No symbol) [0x0x7ff7be6c060f]
+	(No symbol) [0x0x7ff7be718854]
+	(No symbol) [0x0x7ff7be718b1c]
+	(No symbol) [0x0x7ff7be76c927]
+	(No symbol) [0x0x7ff7be74126f]
+	(No symbol) [0x0x7ff7be76968a]
+	(No symbol) [0x0x7ff7be741003]
+	(No symbol) [0x0x7ff7be7095d1]
+	(No symbol) [0x0x7ff7be70a3f3]
+	GetHandleVerifier [0x0x7ff7bebfdd0d+2960461]
+	GetHandleVerifier [0x0x7ff7bebf7fca+2936586]
+	GetHandleVerifier [0x0x7ff7bec18a07+3070279]
+	GetHandleVerifier [0x0x7ff7be95843e+185214]
+	GetHandleVerifier [0x0x7ff7be95fe8f+216527]
+	GetHandleVerifier [0x0x7ff7be947b94+117460]
+	GetHandleVerifier [0x0x7ff7be947d4f+117903]
+	GetHandleVerifier [0x0x7ff7be92dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1080,25 +1080,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7799ae955+80021]
-	GetHandleVerifier [0x0x7ff7799ae9b0+80112]
-	(No symbol) [0x0x7ff77973060f]
-	(No symbol) [0x0x7ff779788854]
-	(No symbol) [0x0x7ff779788b1c]
-	(No symbol) [0x0x7ff7797dc927]
-	(No symbol) [0x0x7ff7797b126f]
-	(No symbol) [0x0x7ff7797d968a]
-	(No symbol) [0x0x7ff7797b1003]
-	(No symbol) [0x0x7ff7797795d1]
-	(No symbol) [0x0x7ff77977a3f3]
-	GetHandleVerifier [0x0x7ff779c6dd0d+2960461]
-	GetHandleVerifier [0x0x7ff779c67fca+2936586]
-	GetHandleVerifier [0x0x7ff779c88a07+3070279]
-	GetHandleVerifier [0x0x7ff7799c843e+185214]
-	GetHandleVerifier [0x0x7ff7799cfe8f+216527]
-	GetHandleVerifier [0x0x7ff7799b7b94+117460]
-	GetHandleVerifier [0x0x7ff7799b7d4f+117903]
-	GetHandleVerifier [0x0x7ff77999dc28+11112]
+	GetHandleVerifier [0x0x7ff7be93e955+80021]
+	GetHandleVerifier [0x0x7ff7be93e9b0+80112]
+	(No symbol) [0x0x7ff7be6c060f]
+	(No symbol) [0x0x7ff7be718854]
+	(No symbol) [0x0x7ff7be718b1c]
+	(No symbol) [0x0x7ff7be76c927]
+	(No symbol) [0x0x7ff7be74126f]
+	(No symbol) [0x0x7ff7be76968a]
+	(No symbol) [0x0x7ff7be741003]
+	(No symbol) [0x0x7ff7be7095d1]
+	(No symbol) [0x0x7ff7be70a3f3]
+	GetHandleVerifier [0x0x7ff7bebfdd0d+2960461]
+	GetHandleVerifier [0x0x7ff7bebf7fca+2936586]
+	GetHandleVerifier [0x0x7ff7bec18a07+3070279]
+	GetHandleVerifier [0x0x7ff7be95843e+185214]
+	GetHandleVerifier [0x0x7ff7be95fe8f+216527]
+	GetHandleVerifier [0x0x7ff7be947b94+117460]
+	GetHandleVerifier [0x0x7ff7be947d4f+117903]
+	GetHandleVerifier [0x0x7ff7be92dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1202,25 +1202,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7799ae955+80021]
-	GetHandleVerifier [0x0x7ff7799ae9b0+80112]
-	(No symbol) [0x0x7ff77973060f]
-	(No symbol) [0x0x7ff779788854]
-	(No symbol) [0x0x7ff779788b1c]
-	(No symbol) [0x0x7ff7797dc927]
-	(No symbol) [0x0x7ff7797b126f]
-	(No symbol) [0x0x7ff7797d968a]
-	(No symbol) [0x0x7ff7797b1003]
-	(No symbol) [0x0x7ff7797795d1]
-	(No symbol) [0x0x7ff77977a3f3]
-	GetHandleVerifier [0x0x7ff779c6dd0d+2960461]
-	GetHandleVerifier [0x0x7ff779c67fca+2936586]
-	GetHandleVerifier [0x0x7ff779c88a07+3070279]
-	GetHandleVerifier [0x0x7ff7799c843e+185214]
-	GetHandleVerifier [0x0x7ff7799cfe8f+216527]
-	GetHandleVerifier [0x0x7ff7799b7b94+117460]
-	GetHandleVerifier [0x0x7ff7799b7d4f+117903]
-	GetHandleVerifier [0x0x7ff77999dc28+11112]
+	GetHandleVerifier [0x0x7ff7be93e955+80021]
+	GetHandleVerifier [0x0x7ff7be93e9b0+80112]
+	(No symbol) [0x0x7ff7be6c060f]
+	(No symbol) [0x0x7ff7be718854]
+	(No symbol) [0x0x7ff7be718b1c]
+	(No symbol) [0x0x7ff7be76c927]
+	(No symbol) [0x0x7ff7be74126f]
+	(No symbol) [0x0x7ff7be76968a]
+	(No symbol) [0x0x7ff7be741003]
+	(No symbol) [0x0x7ff7be7095d1]
+	(No symbol) [0x0x7ff7be70a3f3]
+	GetHandleVerifier [0x0x7ff7bebfdd0d+2960461]
+	GetHandleVerifier [0x0x7ff7bebf7fca+2936586]
+	GetHandleVerifier [0x0x7ff7bec18a07+3070279]
+	GetHandleVerifier [0x0x7ff7be95843e+185214]
+	GetHandleVerifier [0x0x7ff7be95fe8f+216527]
+	GetHandleVerifier [0x0x7ff7be947b94+117460]
+	GetHandleVerifier [0x0x7ff7be947d4f+117903]
+	GetHandleVerifier [0x0x7ff7be92dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1324,25 +1324,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7799ae955+80021]
-	GetHandleVerifier [0x0x7ff7799ae9b0+80112]
-	(No symbol) [0x0x7ff77973060f]
-	(No symbol) [0x0x7ff779788854]
-	(No symbol) [0x0x7ff779788b1c]
-	(No symbol) [0x0x7ff7797dc927]
-	(No symbol) [0x0x7ff7797b126f]
-	(No symbol) [0x0x7ff7797d968a]
-	(No symbol) [0x0x7ff7797b1003]
-	(No symbol) [0x0x7ff7797795d1]
-	(No symbol) [0x0x7ff77977a3f3]
-	GetHandleVerifier [0x0x7ff779c6dd0d+2960461]
-	GetHandleVerifier [0x0x7ff779c67fca+2936586]
-	GetHandleVerifier [0x0x7ff779c88a07+3070279]
-	GetHandleVerifier [0x0x7ff7799c843e+185214]
-	GetHandleVerifier [0x0x7ff7799cfe8f+216527]
-	GetHandleVerifier [0x0x7ff7799b7b94+117460]
-	GetHandleVerifier [0x0x7ff7799b7d4f+117903]
-	GetHandleVerifier [0x0x7ff77999dc28+11112]
+	GetHandleVerifier [0x0x7ff7be93e955+80021]
+	GetHandleVerifier [0x0x7ff7be93e9b0+80112]
+	(No symbol) [0x0x7ff7be6c060f]
+	(No symbol) [0x0x7ff7be718854]
+	(No symbol) [0x0x7ff7be718b1c]
+	(No symbol) [0x0x7ff7be76c927]
+	(No symbol) [0x0x7ff7be74126f]
+	(No symbol) [0x0x7ff7be76968a]
+	(No symbol) [0x0x7ff7be741003]
+	(No symbol) [0x0x7ff7be7095d1]
+	(No symbol) [0x0x7ff7be70a3f3]
+	GetHandleVerifier [0x0x7ff7bebfdd0d+2960461]
+	GetHandleVerifier [0x0x7ff7bebf7fca+2936586]
+	GetHandleVerifier [0x0x7ff7bec18a07+3070279]
+	GetHandleVerifier [0x0x7ff7be95843e+185214]
+	GetHandleVerifier [0x0x7ff7be95fe8f+216527]
+	GetHandleVerifier [0x0x7ff7be947b94+117460]
+	GetHandleVerifier [0x0x7ff7be947d4f+117903]
+	GetHandleVerifier [0x0x7ff7be92dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1446,25 +1446,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7799ae955+80021]
-	GetHandleVerifier [0x0x7ff7799ae9b0+80112]
-	(No symbol) [0x0x7ff77973060f]
-	(No symbol) [0x0x7ff779788854]
-	(No symbol) [0x0x7ff779788b1c]
-	(No symbol) [0x0x7ff7797dc927]
-	(No symbol) [0x0x7ff7797b126f]
-	(No symbol) [0x0x7ff7797d968a]
-	(No symbol) [0x0x7ff7797b1003]
-	(No symbol) [0x0x7ff7797795d1]
-	(No symbol) [0x0x7ff77977a3f3]
-	GetHandleVerifier [0x0x7ff779c6dd0d+2960461]
-	GetHandleVerifier [0x0x7ff779c67fca+2936586]
-	GetHandleVerifier [0x0x7ff779c88a07+3070279]
-	GetHandleVerifier [0x0x7ff7799c843e+185214]
-	GetHandleVerifier [0x0x7ff7799cfe8f+216527]
-	GetHandleVerifier [0x0x7ff7799b7b94+117460]
-	GetHandleVerifier [0x0x7ff7799b7d4f+117903]
-	GetHandleVerifier [0x0x7ff77999dc28+11112]
+	GetHandleVerifier [0x0x7ff7be93e955+80021]
+	GetHandleVerifier [0x0x7ff7be93e9b0+80112]
+	(No symbol) [0x0x7ff7be6c060f]
+	(No symbol) [0x0x7ff7be718854]
+	(No symbol) [0x0x7ff7be718b1c]
+	(No symbol) [0x0x7ff7be76c927]
+	(No symbol) [0x0x7ff7be74126f]
+	(No symbol) [0x0x7ff7be76968a]
+	(No symbol) [0x0x7ff7be741003]
+	(No symbol) [0x0x7ff7be7095d1]
+	(No symbol) [0x0x7ff7be70a3f3]
+	GetHandleVerifier [0x0x7ff7bebfdd0d+2960461]
+	GetHandleVerifier [0x0x7ff7bebf7fca+2936586]
+	GetHandleVerifier [0x0x7ff7bec18a07+3070279]
+	GetHandleVerifier [0x0x7ff7be95843e+185214]
+	GetHandleVerifier [0x0x7ff7be95fe8f+216527]
+	GetHandleVerifier [0x0x7ff7be947b94+117460]
+	GetHandleVerifier [0x0x7ff7be947d4f+117903]
+	GetHandleVerifier [0x0x7ff7be92dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1568,25 +1568,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7799ae955+80021]
-	GetHandleVerifier [0x0x7ff7799ae9b0+80112]
-	(No symbol) [0x0x7ff77973060f]
-	(No symbol) [0x0x7ff779788854]
-	(No symbol) [0x0x7ff779788b1c]
-	(No symbol) [0x0x7ff7797dc927]
-	(No symbol) [0x0x7ff7797b126f]
-	(No symbol) [0x0x7ff7797d968a]
-	(No symbol) [0x0x7ff7797b1003]
-	(No symbol) [0x0x7ff7797795d1]
-	(No symbol) [0x0x7ff77977a3f3]
-	GetHandleVerifier [0x0x7ff779c6dd0d+2960461]
-	GetHandleVerifier [0x0x7ff779c67fca+2936586]
-	GetHandleVerifier [0x0x7ff779c88a07+3070279]
-	GetHandleVerifier [0x0x7ff7799c843e+185214]
-	GetHandleVerifier [0x0x7ff7799cfe8f+216527]
-	GetHandleVerifier [0x0x7ff7799b7b94+117460]
-	GetHandleVerifier [0x0x7ff7799b7d4f+117903]
-	GetHandleVerifier [0x0x7ff77999dc28+11112]
+	GetHandleVerifier [0x0x7ff7be93e955+80021]
+	GetHandleVerifier [0x0x7ff7be93e9b0+80112]
+	(No symbol) [0x0x7ff7be6c060f]
+	(No symbol) [0x0x7ff7be718854]
+	(No symbol) [0x0x7ff7be718b1c]
+	(No symbol) [0x0x7ff7be76c927]
+	(No symbol) [0x0x7ff7be74126f]
+	(No symbol) [0x0x7ff7be76968a]
+	(No symbol) [0x0x7ff7be741003]
+	(No symbol) [0x0x7ff7be7095d1]
+	(No symbol) [0x0x7ff7be70a3f3]
+	GetHandleVerifier [0x0x7ff7bebfdd0d+2960461]
+	GetHandleVerifier [0x0x7ff7bebf7fca+2936586]
+	GetHandleVerifier [0x0x7ff7bec18a07+3070279]
+	GetHandleVerifier [0x0x7ff7be95843e+185214]
+	GetHandleVerifier [0x0x7ff7be95fe8f+216527]
+	GetHandleVerifier [0x0x7ff7be947b94+117460]
+	GetHandleVerifier [0x0x7ff7be947d4f+117903]
+	GetHandleVerifier [0x0x7ff7be92dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1690,25 +1690,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7799ae955+80021]
-	GetHandleVerifier [0x0x7ff7799ae9b0+80112]
-	(No symbol) [0x0x7ff77973060f]
-	(No symbol) [0x0x7ff779788854]
-	(No symbol) [0x0x7ff779788b1c]
-	(No symbol) [0x0x7ff7797dc927]
-	(No symbol) [0x0x7ff7797b126f]
-	(No symbol) [0x0x7ff7797d968a]
-	(No symbol) [0x0x7ff7797b1003]
-	(No symbol) [0x0x7ff7797795d1]
-	(No symbol) [0x0x7ff77977a3f3]
-	GetHandleVerifier [0x0x7ff779c6dd0d+2960461]
-	GetHandleVerifier [0x0x7ff779c67fca+2936586]
-	GetHandleVerifier [0x0x7ff779c88a07+3070279]
-	GetHandleVerifier [0x0x7ff7799c843e+185214]
-	GetHandleVerifier [0x0x7ff7799cfe8f+216527]
-	GetHandleVerifier [0x0x7ff7799b7b94+117460]
-	GetHandleVerifier [0x0x7ff7799b7d4f+117903]
-	GetHandleVerifier [0x0x7ff77999dc28+11112]
+	GetHandleVerifier [0x0x7ff7be93e955+80021]
+	GetHandleVerifier [0x0x7ff7be93e9b0+80112]
+	(No symbol) [0x0x7ff7be6c060f]
+	(No symbol) [0x0x7ff7be718854]
+	(No symbol) [0x0x7ff7be718b1c]
+	(No symbol) [0x0x7ff7be76c927]
+	(No symbol) [0x0x7ff7be74126f]
+	(No symbol) [0x0x7ff7be76968a]
+	(No symbol) [0x0x7ff7be741003]
+	(No symbol) [0x0x7ff7be7095d1]
+	(No symbol) [0x0x7ff7be70a3f3]
+	GetHandleVerifier [0x0x7ff7bebfdd0d+2960461]
+	GetHandleVerifier [0x0x7ff7bebf7fca+2936586]
+	GetHandleVerifier [0x0x7ff7bec18a07+3070279]
+	GetHandleVerifier [0x0x7ff7be95843e+185214]
+	GetHandleVerifier [0x0x7ff7be95fe8f+216527]
+	GetHandleVerifier [0x0x7ff7be947b94+117460]
+	GetHandleVerifier [0x0x7ff7be947d4f+117903]
+	GetHandleVerifier [0x0x7ff7be92dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1812,25 +1812,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7799ae955+80021]
-	GetHandleVerifier [0x0x7ff7799ae9b0+80112]
-	(No symbol) [0x0x7ff77973060f]
-	(No symbol) [0x0x7ff779788854]
-	(No symbol) [0x0x7ff779788b1c]
-	(No symbol) [0x0x7ff7797dc927]
-	(No symbol) [0x0x7ff7797b126f]
-	(No symbol) [0x0x7ff7797d968a]
-	(No symbol) [0x0x7ff7797b1003]
-	(No symbol) [0x0x7ff7797795d1]
-	(No symbol) [0x0x7ff77977a3f3]
-	GetHandleVerifier [0x0x7ff779c6dd0d+2960461]
-	GetHandleVerifier [0x0x7ff779c67fca+2936586]
-	GetHandleVerifier [0x0x7ff779c88a07+3070279]
-	GetHandleVerifier [0x0x7ff7799c843e+185214]
-	GetHandleVerifier [0x0x7ff7799cfe8f+216527]
-	GetHandleVerifier [0x0x7ff7799b7b94+117460]
-	GetHandleVerifier [0x0x7ff7799b7d4f+117903]
-	GetHandleVerifier [0x0x7ff77999dc28+11112]
+	GetHandleVerifier [0x0x7ff7be93e955+80021]
+	GetHandleVerifier [0x0x7ff7be93e9b0+80112]
+	(No symbol) [0x0x7ff7be6c060f]
+	(No symbol) [0x0x7ff7be718854]
+	(No symbol) [0x0x7ff7be718b1c]
+	(No symbol) [0x0x7ff7be76c927]
+	(No symbol) [0x0x7ff7be74126f]
+	(No symbol) [0x0x7ff7be76968a]
+	(No symbol) [0x0x7ff7be741003]
+	(No symbol) [0x0x7ff7be7095d1]
+	(No symbol) [0x0x7ff7be70a3f3]
+	GetHandleVerifier [0x0x7ff7bebfdd0d+2960461]
+	GetHandleVerifier [0x0x7ff7bebf7fca+2936586]
+	GetHandleVerifier [0x0x7ff7bec18a07+3070279]
+	GetHandleVerifier [0x0x7ff7be95843e+185214]
+	GetHandleVerifier [0x0x7ff7be95fe8f+216527]
+	GetHandleVerifier [0x0x7ff7be947b94+117460]
+	GetHandleVerifier [0x0x7ff7be947d4f+117903]
+	GetHandleVerifier [0x0x7ff7be92dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -1934,25 +1934,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7799ae955+80021]
-	GetHandleVerifier [0x0x7ff7799ae9b0+80112]
-	(No symbol) [0x0x7ff77973060f]
-	(No symbol) [0x0x7ff779788854]
-	(No symbol) [0x0x7ff779788b1c]
-	(No symbol) [0x0x7ff7797dc927]
-	(No symbol) [0x0x7ff7797b126f]
-	(No symbol) [0x0x7ff7797d968a]
-	(No symbol) [0x0x7ff7797b1003]
-	(No symbol) [0x0x7ff7797795d1]
-	(No symbol) [0x0x7ff77977a3f3]
-	GetHandleVerifier [0x0x7ff779c6dd0d+2960461]
-	GetHandleVerifier [0x0x7ff779c67fca+2936586]
-	GetHandleVerifier [0x0x7ff779c88a07+3070279]
-	GetHandleVerifier [0x0x7ff7799c843e+185214]
-	GetHandleVerifier [0x0x7ff7799cfe8f+216527]
-	GetHandleVerifier [0x0x7ff7799b7b94+117460]
-	GetHandleVerifier [0x0x7ff7799b7d4f+117903]
-	GetHandleVerifier [0x0x7ff77999dc28+11112]
+	GetHandleVerifier [0x0x7ff7be93e955+80021]
+	GetHandleVerifier [0x0x7ff7be93e9b0+80112]
+	(No symbol) [0x0x7ff7be6c060f]
+	(No symbol) [0x0x7ff7be718854]
+	(No symbol) [0x0x7ff7be718b1c]
+	(No symbol) [0x0x7ff7be76c927]
+	(No symbol) [0x0x7ff7be74126f]
+	(No symbol) [0x0x7ff7be76968a]
+	(No symbol) [0x0x7ff7be741003]
+	(No symbol) [0x0x7ff7be7095d1]
+	(No symbol) [0x0x7ff7be70a3f3]
+	GetHandleVerifier [0x0x7ff7bebfdd0d+2960461]
+	GetHandleVerifier [0x0x7ff7bebf7fca+2936586]
+	GetHandleVerifier [0x0x7ff7bec18a07+3070279]
+	GetHandleVerifier [0x0x7ff7be95843e+185214]
+	GetHandleVerifier [0x0x7ff7be95fe8f+216527]
+	GetHandleVerifier [0x0x7ff7be947b94+117460]
+	GetHandleVerifier [0x0x7ff7be947d4f+117903]
+	GetHandleVerifier [0x0x7ff7be92dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2056,25 +2056,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7799ae955+80021]
-	GetHandleVerifier [0x0x7ff7799ae9b0+80112]
-	(No symbol) [0x0x7ff77973060f]
-	(No symbol) [0x0x7ff779788854]
-	(No symbol) [0x0x7ff779788b1c]
-	(No symbol) [0x0x7ff7797dc927]
-	(No symbol) [0x0x7ff7797b126f]
-	(No symbol) [0x0x7ff7797d968a]
-	(No symbol) [0x0x7ff7797b1003]
-	(No symbol) [0x0x7ff7797795d1]
-	(No symbol) [0x0x7ff77977a3f3]
-	GetHandleVerifier [0x0x7ff779c6dd0d+2960461]
-	GetHandleVerifier [0x0x7ff779c67fca+2936586]
-	GetHandleVerifier [0x0x7ff779c88a07+3070279]
-	GetHandleVerifier [0x0x7ff7799c843e+185214]
-	GetHandleVerifier [0x0x7ff7799cfe8f+216527]
-	GetHandleVerifier [0x0x7ff7799b7b94+117460]
-	GetHandleVerifier [0x0x7ff7799b7d4f+117903]
-	GetHandleVerifier [0x0x7ff77999dc28+11112]
+	GetHandleVerifier [0x0x7ff7be93e955+80021]
+	GetHandleVerifier [0x0x7ff7be93e9b0+80112]
+	(No symbol) [0x0x7ff7be6c060f]
+	(No symbol) [0x0x7ff7be718854]
+	(No symbol) [0x0x7ff7be718b1c]
+	(No symbol) [0x0x7ff7be76c927]
+	(No symbol) [0x0x7ff7be74126f]
+	(No symbol) [0x0x7ff7be76968a]
+	(No symbol) [0x0x7ff7be741003]
+	(No symbol) [0x0x7ff7be7095d1]
+	(No symbol) [0x0x7ff7be70a3f3]
+	GetHandleVerifier [0x0x7ff7bebfdd0d+2960461]
+	GetHandleVerifier [0x0x7ff7bebf7fca+2936586]
+	GetHandleVerifier [0x0x7ff7bec18a07+3070279]
+	GetHandleVerifier [0x0x7ff7be95843e+185214]
+	GetHandleVerifier [0x0x7ff7be95fe8f+216527]
+	GetHandleVerifier [0x0x7ff7be947b94+117460]
+	GetHandleVerifier [0x0x7ff7be947d4f+117903]
+	GetHandleVerifier [0x0x7ff7be92dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2177,25 +2177,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7799ae955+80021]
-	GetHandleVerifier [0x0x7ff7799ae9b0+80112]
-	(No symbol) [0x0x7ff77973060f]
-	(No symbol) [0x0x7ff779788854]
-	(No symbol) [0x0x7ff779788b1c]
-	(No symbol) [0x0x7ff7797dc927]
-	(No symbol) [0x0x7ff7797b126f]
-	(No symbol) [0x0x7ff7797d968a]
-	(No symbol) [0x0x7ff7797b1003]
-	(No symbol) [0x0x7ff7797795d1]
-	(No symbol) [0x0x7ff77977a3f3]
-	GetHandleVerifier [0x0x7ff779c6dd0d+2960461]
-	GetHandleVerifier [0x0x7ff779c67fca+2936586]
-	GetHandleVerifier [0x0x7ff779c88a07+3070279]
-	GetHandleVerifier [0x0x7ff7799c843e+185214]
-	GetHandleVerifier [0x0x7ff7799cfe8f+216527]
-	GetHandleVerifier [0x0x7ff7799b7b94+117460]
-	GetHandleVerifier [0x0x7ff7799b7d4f+117903]
-	GetHandleVerifier [0x0x7ff77999dc28+11112]
+	GetHandleVerifier [0x0x7ff7be93e955+80021]
+	GetHandleVerifier [0x0x7ff7be93e9b0+80112]
+	(No symbol) [0x0x7ff7be6c060f]
+	(No symbol) [0x0x7ff7be718854]
+	(No symbol) [0x0x7ff7be718b1c]
+	(No symbol) [0x0x7ff7be76c927]
+	(No symbol) [0x0x7ff7be74126f]
+	(No symbol) [0x0x7ff7be76968a]
+	(No symbol) [0x0x7ff7be741003]
+	(No symbol) [0x0x7ff7be7095d1]
+	(No symbol) [0x0x7ff7be70a3f3]
+	GetHandleVerifier [0x0x7ff7bebfdd0d+2960461]
+	GetHandleVerifier [0x0x7ff7bebf7fca+2936586]
+	GetHandleVerifier [0x0x7ff7bec18a07+3070279]
+	GetHandleVerifier [0x0x7ff7be95843e+185214]
+	GetHandleVerifier [0x0x7ff7be95fe8f+216527]
+	GetHandleVerifier [0x0x7ff7be947b94+117460]
+	GetHandleVerifier [0x0x7ff7be947d4f+117903]
+	GetHandleVerifier [0x0x7ff7be92dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2299,25 +2299,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7799ae955+80021]
-	GetHandleVerifier [0x0x7ff7799ae9b0+80112]
-	(No symbol) [0x0x7ff77973060f]
-	(No symbol) [0x0x7ff779788854]
-	(No symbol) [0x0x7ff779788b1c]
-	(No symbol) [0x0x7ff7797dc927]
-	(No symbol) [0x0x7ff7797b126f]
-	(No symbol) [0x0x7ff7797d968a]
-	(No symbol) [0x0x7ff7797b1003]
-	(No symbol) [0x0x7ff7797795d1]
-	(No symbol) [0x0x7ff77977a3f3]
-	GetHandleVerifier [0x0x7ff779c6dd0d+2960461]
-	GetHandleVerifier [0x0x7ff779c67fca+2936586]
-	GetHandleVerifier [0x0x7ff779c88a07+3070279]
-	GetHandleVerifier [0x0x7ff7799c843e+185214]
-	GetHandleVerifier [0x0x7ff7799cfe8f+216527]
-	GetHandleVerifier [0x0x7ff7799b7b94+117460]
-	GetHandleVerifier [0x0x7ff7799b7d4f+117903]
-	GetHandleVerifier [0x0x7ff77999dc28+11112]
+	GetHandleVerifier [0x0x7ff7be93e955+80021]
+	GetHandleVerifier [0x0x7ff7be93e9b0+80112]
+	(No symbol) [0x0x7ff7be6c060f]
+	(No symbol) [0x0x7ff7be718854]
+	(No symbol) [0x0x7ff7be718b1c]
+	(No symbol) [0x0x7ff7be76c927]
+	(No symbol) [0x0x7ff7be74126f]
+	(No symbol) [0x0x7ff7be76968a]
+	(No symbol) [0x0x7ff7be741003]
+	(No symbol) [0x0x7ff7be7095d1]
+	(No symbol) [0x0x7ff7be70a3f3]
+	GetHandleVerifier [0x0x7ff7bebfdd0d+2960461]
+	GetHandleVerifier [0x0x7ff7bebf7fca+2936586]
+	GetHandleVerifier [0x0x7ff7bec18a07+3070279]
+	GetHandleVerifier [0x0x7ff7be95843e+185214]
+	GetHandleVerifier [0x0x7ff7be95fe8f+216527]
+	GetHandleVerifier [0x0x7ff7be947b94+117460]
+	GetHandleVerifier [0x0x7ff7be947d4f+117903]
+	GetHandleVerifier [0x0x7ff7be92dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2519,25 +2519,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7799ae955+80021]
-	GetHandleVerifier [0x0x7ff7799ae9b0+80112]
-	(No symbol) [0x0x7ff77973060f]
-	(No symbol) [0x0x7ff779788854]
-	(No symbol) [0x0x7ff779788b1c]
-	(No symbol) [0x0x7ff7797dc927]
-	(No symbol) [0x0x7ff7797b126f]
-	(No symbol) [0x0x7ff7797d968a]
-	(No symbol) [0x0x7ff7797b1003]
-	(No symbol) [0x0x7ff7797795d1]
-	(No symbol) [0x0x7ff77977a3f3]
-	GetHandleVerifier [0x0x7ff779c6dd0d+2960461]
-	GetHandleVerifier [0x0x7ff779c67fca+2936586]
-	GetHandleVerifier [0x0x7ff779c88a07+3070279]
-	GetHandleVerifier [0x0x7ff7799c843e+185214]
-	GetHandleVerifier [0x0x7ff7799cfe8f+216527]
-	GetHandleVerifier [0x0x7ff7799b7b94+117460]
-	GetHandleVerifier [0x0x7ff7799b7d4f+117903]
-	GetHandleVerifier [0x0x7ff77999dc28+11112]
+	GetHandleVerifier [0x0x7ff7be93e955+80021]
+	GetHandleVerifier [0x0x7ff7be93e9b0+80112]
+	(No symbol) [0x0x7ff7be6c060f]
+	(No symbol) [0x0x7ff7be718854]
+	(No symbol) [0x0x7ff7be718b1c]
+	(No symbol) [0x0x7ff7be76c927]
+	(No symbol) [0x0x7ff7be74126f]
+	(No symbol) [0x0x7ff7be76968a]
+	(No symbol) [0x0x7ff7be741003]
+	(No symbol) [0x0x7ff7be7095d1]
+	(No symbol) [0x0x7ff7be70a3f3]
+	GetHandleVerifier [0x0x7ff7bebfdd0d+2960461]
+	GetHandleVerifier [0x0x7ff7bebf7fca+2936586]
+	GetHandleVerifier [0x0x7ff7bec18a07+3070279]
+	GetHandleVerifier [0x0x7ff7be95843e+185214]
+	GetHandleVerifier [0x0x7ff7be95fe8f+216527]
+	GetHandleVerifier [0x0x7ff7be947b94+117460]
+	GetHandleVerifier [0x0x7ff7be947d4f+117903]
+	GetHandleVerifier [0x0x7ff7be92dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2640,25 +2640,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7799ae955+80021]
-	GetHandleVerifier [0x0x7ff7799ae9b0+80112]
-	(No symbol) [0x0x7ff77973060f]
-	(No symbol) [0x0x7ff779788854]
-	(No symbol) [0x0x7ff779788b1c]
-	(No symbol) [0x0x7ff7797dc927]
-	(No symbol) [0x0x7ff7797b126f]
-	(No symbol) [0x0x7ff7797d968a]
-	(No symbol) [0x0x7ff7797b1003]
-	(No symbol) [0x0x7ff7797795d1]
-	(No symbol) [0x0x7ff77977a3f3]
-	GetHandleVerifier [0x0x7ff779c6dd0d+2960461]
-	GetHandleVerifier [0x0x7ff779c67fca+2936586]
-	GetHandleVerifier [0x0x7ff779c88a07+3070279]
-	GetHandleVerifier [0x0x7ff7799c843e+185214]
-	GetHandleVerifier [0x0x7ff7799cfe8f+216527]
-	GetHandleVerifier [0x0x7ff7799b7b94+117460]
-	GetHandleVerifier [0x0x7ff7799b7d4f+117903]
-	GetHandleVerifier [0x0x7ff77999dc28+11112]
+	GetHandleVerifier [0x0x7ff7be93e955+80021]
+	GetHandleVerifier [0x0x7ff7be93e9b0+80112]
+	(No symbol) [0x0x7ff7be6c060f]
+	(No symbol) [0x0x7ff7be718854]
+	(No symbol) [0x0x7ff7be718b1c]
+	(No symbol) [0x0x7ff7be76c927]
+	(No symbol) [0x0x7ff7be74126f]
+	(No symbol) [0x0x7ff7be76968a]
+	(No symbol) [0x0x7ff7be741003]
+	(No symbol) [0x0x7ff7be7095d1]
+	(No symbol) [0x0x7ff7be70a3f3]
+	GetHandleVerifier [0x0x7ff7bebfdd0d+2960461]
+	GetHandleVerifier [0x0x7ff7bebf7fca+2936586]
+	GetHandleVerifier [0x0x7ff7bec18a07+3070279]
+	GetHandleVerifier [0x0x7ff7be95843e+185214]
+	GetHandleVerifier [0x0x7ff7be95fe8f+216527]
+	GetHandleVerifier [0x0x7ff7be947b94+117460]
+	GetHandleVerifier [0x0x7ff7be947d4f+117903]
+	GetHandleVerifier [0x0x7ff7be92dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2761,25 +2761,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7799ae955+80021]
-	GetHandleVerifier [0x0x7ff7799ae9b0+80112]
-	(No symbol) [0x0x7ff77973060f]
-	(No symbol) [0x0x7ff779788854]
-	(No symbol) [0x0x7ff779788b1c]
-	(No symbol) [0x0x7ff7797dc927]
-	(No symbol) [0x0x7ff7797b126f]
-	(No symbol) [0x0x7ff7797d968a]
-	(No symbol) [0x0x7ff7797b1003]
-	(No symbol) [0x0x7ff7797795d1]
-	(No symbol) [0x0x7ff77977a3f3]
-	GetHandleVerifier [0x0x7ff779c6dd0d+2960461]
-	GetHandleVerifier [0x0x7ff779c67fca+2936586]
-	GetHandleVerifier [0x0x7ff779c88a07+3070279]
-	GetHandleVerifier [0x0x7ff7799c843e+185214]
-	GetHandleVerifier [0x0x7ff7799cfe8f+216527]
-	GetHandleVerifier [0x0x7ff7799b7b94+117460]
-	GetHandleVerifier [0x0x7ff7799b7d4f+117903]
-	GetHandleVerifier [0x0x7ff77999dc28+11112]
+	GetHandleVerifier [0x0x7ff7be93e955+80021]
+	GetHandleVerifier [0x0x7ff7be93e9b0+80112]
+	(No symbol) [0x0x7ff7be6c060f]
+	(No symbol) [0x0x7ff7be718854]
+	(No symbol) [0x0x7ff7be718b1c]
+	(No symbol) [0x0x7ff7be76c927]
+	(No symbol) [0x0x7ff7be74126f]
+	(No symbol) [0x0x7ff7be76968a]
+	(No symbol) [0x0x7ff7be741003]
+	(No symbol) [0x0x7ff7be7095d1]
+	(No symbol) [0x0x7ff7be70a3f3]
+	GetHandleVerifier [0x0x7ff7bebfdd0d+2960461]
+	GetHandleVerifier [0x0x7ff7bebf7fca+2936586]
+	GetHandleVerifier [0x0x7ff7bec18a07+3070279]
+	GetHandleVerifier [0x0x7ff7be95843e+185214]
+	GetHandleVerifier [0x0x7ff7be95fe8f+216527]
+	GetHandleVerifier [0x0x7ff7be947b94+117460]
+	GetHandleVerifier [0x0x7ff7be947d4f+117903]
+	GetHandleVerifier [0x0x7ff7be92dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -2882,25 +2882,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7799ae955+80021]
-	GetHandleVerifier [0x0x7ff7799ae9b0+80112]
-	(No symbol) [0x0x7ff77973060f]
-	(No symbol) [0x0x7ff779788854]
-	(No symbol) [0x0x7ff779788b1c]
-	(No symbol) [0x0x7ff7797dc927]
-	(No symbol) [0x0x7ff7797b126f]
-	(No symbol) [0x0x7ff7797d968a]
-	(No symbol) [0x0x7ff7797b1003]
-	(No symbol) [0x0x7ff7797795d1]
-	(No symbol) [0x0x7ff77977a3f3]
-	GetHandleVerifier [0x0x7ff779c6dd0d+2960461]
-	GetHandleVerifier [0x0x7ff779c67fca+2936586]
-	GetHandleVerifier [0x0x7ff779c88a07+3070279]
-	GetHandleVerifier [0x0x7ff7799c843e+185214]
-	GetHandleVerifier [0x0x7ff7799cfe8f+216527]
-	GetHandleVerifier [0x0x7ff7799b7b94+117460]
-	GetHandleVerifier [0x0x7ff7799b7d4f+117903]
-	GetHandleVerifier [0x0x7ff77999dc28+11112]
+	GetHandleVerifier [0x0x7ff7be93e955+80021]
+	GetHandleVerifier [0x0x7ff7be93e9b0+80112]
+	(No symbol) [0x0x7ff7be6c060f]
+	(No symbol) [0x0x7ff7be718854]
+	(No symbol) [0x0x7ff7be718b1c]
+	(No symbol) [0x0x7ff7be76c927]
+	(No symbol) [0x0x7ff7be74126f]
+	(No symbol) [0x0x7ff7be76968a]
+	(No symbol) [0x0x7ff7be741003]
+	(No symbol) [0x0x7ff7be7095d1]
+	(No symbol) [0x0x7ff7be70a3f3]
+	GetHandleVerifier [0x0x7ff7bebfdd0d+2960461]
+	GetHandleVerifier [0x0x7ff7bebf7fca+2936586]
+	GetHandleVerifier [0x0x7ff7bec18a07+3070279]
+	GetHandleVerifier [0x0x7ff7be95843e+185214]
+	GetHandleVerifier [0x0x7ff7be95fe8f+216527]
+	GetHandleVerifier [0x0x7ff7be947b94+117460]
+	GetHandleVerifier [0x0x7ff7be947d4f+117903]
+	GetHandleVerifier [0x0x7ff7be92dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3003,25 +3003,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7799ae955+80021]
-	GetHandleVerifier [0x0x7ff7799ae9b0+80112]
-	(No symbol) [0x0x7ff77973060f]
-	(No symbol) [0x0x7ff779788854]
-	(No symbol) [0x0x7ff779788b1c]
-	(No symbol) [0x0x7ff7797dc927]
-	(No symbol) [0x0x7ff7797b126f]
-	(No symbol) [0x0x7ff7797d968a]
-	(No symbol) [0x0x7ff7797b1003]
-	(No symbol) [0x0x7ff7797795d1]
-	(No symbol) [0x0x7ff77977a3f3]
-	GetHandleVerifier [0x0x7ff779c6dd0d+2960461]
-	GetHandleVerifier [0x0x7ff779c67fca+2936586]
-	GetHandleVerifier [0x0x7ff779c88a07+3070279]
-	GetHandleVerifier [0x0x7ff7799c843e+185214]
-	GetHandleVerifier [0x0x7ff7799cfe8f+216527]
-	GetHandleVerifier [0x0x7ff7799b7b94+117460]
-	GetHandleVerifier [0x0x7ff7799b7d4f+117903]
-	GetHandleVerifier [0x0x7ff77999dc28+11112]
+	GetHandleVerifier [0x0x7ff7be93e955+80021]
+	GetHandleVerifier [0x0x7ff7be93e9b0+80112]
+	(No symbol) [0x0x7ff7be6c060f]
+	(No symbol) [0x0x7ff7be718854]
+	(No symbol) [0x0x7ff7be718b1c]
+	(No symbol) [0x0x7ff7be76c927]
+	(No symbol) [0x0x7ff7be74126f]
+	(No symbol) [0x0x7ff7be76968a]
+	(No symbol) [0x0x7ff7be741003]
+	(No symbol) [0x0x7ff7be7095d1]
+	(No symbol) [0x0x7ff7be70a3f3]
+	GetHandleVerifier [0x0x7ff7bebfdd0d+2960461]
+	GetHandleVerifier [0x0x7ff7bebf7fca+2936586]
+	GetHandleVerifier [0x0x7ff7bec18a07+3070279]
+	GetHandleVerifier [0x0x7ff7be95843e+185214]
+	GetHandleVerifier [0x0x7ff7be95fe8f+216527]
+	GetHandleVerifier [0x0x7ff7be947b94+117460]
+	GetHandleVerifier [0x0x7ff7be947d4f+117903]
+	GetHandleVerifier [0x0x7ff7be92dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3124,25 +3124,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7799ae955+80021]
-	GetHandleVerifier [0x0x7ff7799ae9b0+80112]
-	(No symbol) [0x0x7ff77973060f]
-	(No symbol) [0x0x7ff779788854]
-	(No symbol) [0x0x7ff779788b1c]
-	(No symbol) [0x0x7ff7797dc927]
-	(No symbol) [0x0x7ff7797b126f]
-	(No symbol) [0x0x7ff7797d968a]
-	(No symbol) [0x0x7ff7797b1003]
-	(No symbol) [0x0x7ff7797795d1]
-	(No symbol) [0x0x7ff77977a3f3]
-	GetHandleVerifier [0x0x7ff779c6dd0d+2960461]
-	GetHandleVerifier [0x0x7ff779c67fca+2936586]
-	GetHandleVerifier [0x0x7ff779c88a07+3070279]
-	GetHandleVerifier [0x0x7ff7799c843e+185214]
-	GetHandleVerifier [0x0x7ff7799cfe8f+216527]
-	GetHandleVerifier [0x0x7ff7799b7b94+117460]
-	GetHandleVerifier [0x0x7ff7799b7d4f+117903]
-	GetHandleVerifier [0x0x7ff77999dc28+11112]
+	GetHandleVerifier [0x0x7ff7be93e955+80021]
+	GetHandleVerifier [0x0x7ff7be93e9b0+80112]
+	(No symbol) [0x0x7ff7be6c060f]
+	(No symbol) [0x0x7ff7be718854]
+	(No symbol) [0x0x7ff7be718b1c]
+	(No symbol) [0x0x7ff7be76c927]
+	(No symbol) [0x0x7ff7be74126f]
+	(No symbol) [0x0x7ff7be76968a]
+	(No symbol) [0x0x7ff7be741003]
+	(No symbol) [0x0x7ff7be7095d1]
+	(No symbol) [0x0x7ff7be70a3f3]
+	GetHandleVerifier [0x0x7ff7bebfdd0d+2960461]
+	GetHandleVerifier [0x0x7ff7bebf7fca+2936586]
+	GetHandleVerifier [0x0x7ff7bec18a07+3070279]
+	GetHandleVerifier [0x0x7ff7be95843e+185214]
+	GetHandleVerifier [0x0x7ff7be95fe8f+216527]
+	GetHandleVerifier [0x0x7ff7be947b94+117460]
+	GetHandleVerifier [0x0x7ff7be947d4f+117903]
+	GetHandleVerifier [0x0x7ff7be92dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3245,25 +3245,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7799ae955+80021]
-	GetHandleVerifier [0x0x7ff7799ae9b0+80112]
-	(No symbol) [0x0x7ff77973060f]
-	(No symbol) [0x0x7ff779788854]
-	(No symbol) [0x0x7ff779788b1c]
-	(No symbol) [0x0x7ff7797dc927]
-	(No symbol) [0x0x7ff7797b126f]
-	(No symbol) [0x0x7ff7797d968a]
-	(No symbol) [0x0x7ff7797b1003]
-	(No symbol) [0x0x7ff7797795d1]
-	(No symbol) [0x0x7ff77977a3f3]
-	GetHandleVerifier [0x0x7ff779c6dd0d+2960461]
-	GetHandleVerifier [0x0x7ff779c67fca+2936586]
-	GetHandleVerifier [0x0x7ff779c88a07+3070279]
-	GetHandleVerifier [0x0x7ff7799c843e+185214]
-	GetHandleVerifier [0x0x7ff7799cfe8f+216527]
-	GetHandleVerifier [0x0x7ff7799b7b94+117460]
-	GetHandleVerifier [0x0x7ff7799b7d4f+117903]
-	GetHandleVerifier [0x0x7ff77999dc28+11112]
+	GetHandleVerifier [0x0x7ff7be93e955+80021]
+	GetHandleVerifier [0x0x7ff7be93e9b0+80112]
+	(No symbol) [0x0x7ff7be6c060f]
+	(No symbol) [0x0x7ff7be718854]
+	(No symbol) [0x0x7ff7be718b1c]
+	(No symbol) [0x0x7ff7be76c927]
+	(No symbol) [0x0x7ff7be74126f]
+	(No symbol) [0x0x7ff7be76968a]
+	(No symbol) [0x0x7ff7be741003]
+	(No symbol) [0x0x7ff7be7095d1]
+	(No symbol) [0x0x7ff7be70a3f3]
+	GetHandleVerifier [0x0x7ff7bebfdd0d+2960461]
+	GetHandleVerifier [0x0x7ff7bebf7fca+2936586]
+	GetHandleVerifier [0x0x7ff7bec18a07+3070279]
+	GetHandleVerifier [0x0x7ff7be95843e+185214]
+	GetHandleVerifier [0x0x7ff7be95fe8f+216527]
+	GetHandleVerifier [0x0x7ff7be947b94+117460]
+	GetHandleVerifier [0x0x7ff7be947d4f+117903]
+	GetHandleVerifier [0x0x7ff7be92dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3366,25 +3366,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7799ae955+80021]
-	GetHandleVerifier [0x0x7ff7799ae9b0+80112]
-	(No symbol) [0x0x7ff77973060f]
-	(No symbol) [0x0x7ff779788854]
-	(No symbol) [0x0x7ff779788b1c]
-	(No symbol) [0x0x7ff7797dc927]
-	(No symbol) [0x0x7ff7797b126f]
-	(No symbol) [0x0x7ff7797d968a]
-	(No symbol) [0x0x7ff7797b1003]
-	(No symbol) [0x0x7ff7797795d1]
-	(No symbol) [0x0x7ff77977a3f3]
-	GetHandleVerifier [0x0x7ff779c6dd0d+2960461]
-	GetHandleVerifier [0x0x7ff779c67fca+2936586]
-	GetHandleVerifier [0x0x7ff779c88a07+3070279]
-	GetHandleVerifier [0x0x7ff7799c843e+185214]
-	GetHandleVerifier [0x0x7ff7799cfe8f+216527]
-	GetHandleVerifier [0x0x7ff7799b7b94+117460]
-	GetHandleVerifier [0x0x7ff7799b7d4f+117903]
-	GetHandleVerifier [0x0x7ff77999dc28+11112]
+	GetHandleVerifier [0x0x7ff7be93e955+80021]
+	GetHandleVerifier [0x0x7ff7be93e9b0+80112]
+	(No symbol) [0x0x7ff7be6c060f]
+	(No symbol) [0x0x7ff7be718854]
+	(No symbol) [0x0x7ff7be718b1c]
+	(No symbol) [0x0x7ff7be76c927]
+	(No symbol) [0x0x7ff7be74126f]
+	(No symbol) [0x0x7ff7be76968a]
+	(No symbol) [0x0x7ff7be741003]
+	(No symbol) [0x0x7ff7be7095d1]
+	(No symbol) [0x0x7ff7be70a3f3]
+	GetHandleVerifier [0x0x7ff7bebfdd0d+2960461]
+	GetHandleVerifier [0x0x7ff7bebf7fca+2936586]
+	GetHandleVerifier [0x0x7ff7bec18a07+3070279]
+	GetHandleVerifier [0x0x7ff7be95843e+185214]
+	GetHandleVerifier [0x0x7ff7be95fe8f+216527]
+	GetHandleVerifier [0x0x7ff7be947b94+117460]
+	GetHandleVerifier [0x0x7ff7be947d4f+117903]
+	GetHandleVerifier [0x0x7ff7be92dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
@@ -3487,25 +3487,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.55); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff7799ae955+80021]
-	GetHandleVerifier [0x0x7ff7799ae9b0+80112]
-	(No symbol) [0x0x7ff77973060f]
-	(No symbol) [0x0x7ff779788854]
-	(No symbol) [0x0x7ff779788b1c]
-	(No symbol) [0x0x7ff7797dc927]
-	(No symbol) [0x0x7ff7797b126f]
-	(No symbol) [0x0x7ff7797d968a]
-	(No symbol) [0x0x7ff7797b1003]
-	(No symbol) [0x0x7ff7797795d1]
-	(No symbol) [0x0x7ff77977a3f3]
-	GetHandleVerifier [0x0x7ff779c6dd0d+2960461]
-	GetHandleVerifier [0x0x7ff779c67fca+2936586]
-	GetHandleVerifier [0x0x7ff779c88a07+3070279]
-	GetHandleVerifier [0x0x7ff7799c843e+185214]
-	GetHandleVerifier [0x0x7ff7799cfe8f+216527]
-	GetHandleVerifier [0x0x7ff7799b7b94+117460]
-	GetHandleVerifier [0x0x7ff7799b7d4f+117903]
-	GetHandleVerifier [0x0x7ff77999dc28+11112]
+	GetHandleVerifier [0x0x7ff7be93e955+80021]
+	GetHandleVerifier [0x0x7ff7be93e9b0+80112]
+	(No symbol) [0x0x7ff7be6c060f]
+	(No symbol) [0x0x7ff7be718854]
+	(No symbol) [0x0x7ff7be718b1c]
+	(No symbol) [0x0x7ff7be76c927]
+	(No symbol) [0x0x7ff7be74126f]
+	(No symbol) [0x0x7ff7be76968a]
+	(No symbol) [0x0x7ff7be741003]
+	(No symbol) [0x0x7ff7be7095d1]
+	(No symbol) [0x0x7ff7be70a3f3]
+	GetHandleVerifier [0x0x7ff7bebfdd0d+2960461]
+	GetHandleVerifier [0x0x7ff7bebf7fca+2936586]
+	GetHandleVerifier [0x0x7ff7bec18a07+3070279]
+	GetHandleVerifier [0x0x7ff7be95843e+185214]
+	GetHandleVerifier [0x0x7ff7be95fe8f+216527]
+	GetHandleVerifier [0x0x7ff7be947b94+117460]
+	GetHandleVerifier [0x0x7ff7be947d4f+117903]
+	GetHandleVerifier [0x0x7ff7be92dc28+11112]
 	BaseThreadInitThunk [0x0x7ffc6702e8d7+23]
 	RtlUserThreadStart [0x0x7ffc689e8d9c+44]
 </t>
